--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>id</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>sale</t>
+  </si>
+  <si>
+    <t>dialogueFileName</t>
   </si>
   <si>
     <t>一起打乒乓球吧</t>
@@ -1007,7 +1010,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
     <col min="2" max="2" width="18.0909090909091" customWidth="1"/>
@@ -1015,9 +1018,11 @@
     <col min="7" max="7" width="12.4545454545455" customWidth="1"/>
     <col min="8" max="8" width="11.1818181818182" customWidth="1"/>
     <col min="9" max="9" width="15.5454545454545" customWidth="1"/>
+    <col min="10" max="10" width="19.6363636363636" customWidth="1"/>
+    <col min="11" max="11" width="8.36363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1045,13 +1050,16 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>31001</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1063,15 +1071,15 @@
         <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" ht="29" customHeight="1" spans="1:9">
+    <row r="3" ht="29" customHeight="1" spans="1:10">
       <c r="A3">
         <v>32002</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1083,7 +1091,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1"/>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>id</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>属性三提升20点，下回合属性加成提升50%</t>
+  </si>
+  <si>
+    <t>属性三提升20点，下回合随机获得一张普通功能牌</t>
+  </si>
+  <si>
+    <t>获得属性三（属性一/2）点</t>
   </si>
 </sst>
 </file>
@@ -1007,8 +1013,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="18.0909090909091" customWidth="1"/>
     <col min="6" max="6" width="28.1818181818182" style="1" customWidth="1"/>
@@ -1065,6 +1071,9 @@
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="I2">
+        <v>60</v>
+      </c>
     </row>
     <row r="3" ht="29" customHeight="1" spans="1:9">
       <c r="A3">
@@ -1085,8 +1094,50 @@
       <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="I3">
+        <v>60</v>
+      </c>
     </row>
-    <row r="4" ht="23" customHeight="1"/>
+    <row r="4" ht="34" customHeight="1" spans="1:9">
+      <c r="A4">
+        <v>3203</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>33001</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>id</t>
   </si>
@@ -58,22 +58,40 @@
     <t>sale</t>
   </si>
   <si>
+    <t>nextTurn</t>
+  </si>
+  <si>
     <t>一起打乒乓球吧</t>
   </si>
   <si>
-    <t>属性三提升30点</t>
+    <t>属性三提升{nature3}点</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(30,3)</t>
   </si>
   <si>
     <t>爬爬山</t>
   </si>
   <si>
-    <t>属性三提升20点，下回合属性加成提升50%</t>
-  </si>
-  <si>
-    <t>属性三提升20点，下回合随机获得一张普通功能牌</t>
-  </si>
-  <si>
-    <t>获得属性三（属性一/2）点</t>
+    <t>属性三提升{nature3}点，下回合属性加成提升50%</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(20,3)</t>
+  </si>
+  <si>
+    <t>changeProperty(1.5)</t>
+  </si>
+  <si>
+    <t>属性三提升{nature3}点，下回合随机获得一张普通功能牌</t>
+  </si>
+  <si>
+    <t>addRandomCard(2,1,1)</t>
+  </si>
+  <si>
+    <t>角色获得属性三（角色属性一/2）点</t>
+  </si>
+  <si>
+    <t>addNatureByOther(3,1)</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1031,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="18.0909090909091" customWidth="1"/>
@@ -1023,7 +1041,7 @@
     <col min="9" max="9" width="15.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1051,13 +1069,16 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>31001</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1069,18 +1090,21 @@
         <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
       </c>
       <c r="I2">
         <v>60</v>
       </c>
     </row>
-    <row r="3" ht="29" customHeight="1" spans="1:9">
+    <row r="3" ht="29" customHeight="1" spans="1:10">
       <c r="A3">
         <v>32002</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1092,13 +1116,19 @@
         <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:9">
+    <row r="4" ht="34" customHeight="1" spans="1:10">
       <c r="A4">
         <v>3203</v>
       </c>
@@ -1112,13 +1142,16 @@
         <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I4">
         <v>60</v>
       </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" ht="28" spans="1:10">
       <c r="A5">
         <v>33001</v>
       </c>
@@ -1132,7 +1165,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
       </c>
       <c r="I5">
         <v>120</v>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>属性三提升{nature3}点，下回合属性加成提升50%</t>
-  </si>
-  <si>
-    <t>addNatureAtSum(20,3)</t>
   </si>
   <si>
     <t>changeProperty(1.5)</t>
@@ -1119,13 +1116,13 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:10">
@@ -1142,13 +1139,13 @@
         <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I4">
         <v>60</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:10">
@@ -1165,10 +1162,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
         <v>19</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
       </c>
       <c r="I5">
         <v>120</v>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>id</t>
   </si>
@@ -61,7 +61,10 @@
     <t>nextTurn</t>
   </si>
   <si>
-    <t>一起打乒乓球吧</t>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>风过疏竹</t>
   </si>
   <si>
     <t>属性三提升{nature3}点</t>
@@ -70,7 +73,7 @@
     <t>addNatureAtSum(30,3)</t>
   </si>
   <si>
-    <t>爬爬山</t>
+    <t>春风又生</t>
   </si>
   <si>
     <t>属性三提升{nature3}点，下回合属性加成提升50%</t>
@@ -79,10 +82,16 @@
     <t>changeProperty(1.5)</t>
   </si>
   <si>
+    <t>亭亭如盖</t>
+  </si>
+  <si>
     <t>属性三提升{nature3}点，下回合随机获得一张普通功能牌</t>
   </si>
   <si>
     <t>addRandomCard(2,1,1)</t>
+  </si>
+  <si>
+    <t>一叶知秋</t>
   </si>
   <si>
     <t>角色获得属性三（角色属性一/2）点</t>
@@ -101,13 +110,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -574,137 +589,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -716,6 +731,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1028,7 +1046,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="18.0909090909091" customWidth="1"/>
@@ -1038,7 +1056,7 @@
     <col min="9" max="9" width="15.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1069,13 +1087,16 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" ht="17.5" spans="1:11">
       <c r="A2">
         <v>31001</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1087,21 +1108,21 @@
         <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2">
         <v>60</v>
       </c>
     </row>
-    <row r="3" ht="29" customHeight="1" spans="1:10">
+    <row r="3" ht="29" customHeight="1" spans="1:11">
       <c r="A3">
         <v>32002</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1113,22 +1134,25 @@
         <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:10">
+    <row r="4" ht="34" customHeight="1" spans="1:11">
       <c r="A4">
         <v>3203</v>
       </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C4">
         <v>0</v>
       </c>
@@ -1139,19 +1163,22 @@
         <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I4">
         <v>60</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:10">
+    <row r="5" ht="28" spans="1:11">
       <c r="A5">
         <v>33001</v>
       </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="C5">
         <v>0</v>
       </c>
@@ -1162,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I5">
         <v>120</v>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>Icon</t>
+  </si>
+  <si>
+    <t>dialog</t>
   </si>
   <si>
     <t>风过疏竹</t>
@@ -1046,7 +1049,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="18.0909090909091" customWidth="1"/>
@@ -1054,9 +1057,10 @@
     <col min="7" max="7" width="12.4545454545455" customWidth="1"/>
     <col min="8" max="8" width="11.1818181818182" customWidth="1"/>
     <col min="9" max="9" width="15.5454545454545" customWidth="1"/>
+    <col min="10" max="10" width="17.9090909090909" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1090,13 +1094,16 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" ht="17.5" spans="1:11">
+    <row r="2" ht="17.5" spans="1:12">
       <c r="A2">
         <v>31001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1108,21 +1115,24 @@
         <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2">
         <v>60</v>
       </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" ht="29" customHeight="1" spans="1:11">
+    <row r="3" ht="29" customHeight="1" spans="1:12">
       <c r="A3">
         <v>32002</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1134,24 +1144,27 @@
         <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:11">
+    <row r="4" ht="34" customHeight="1" spans="1:12">
       <c r="A4">
         <v>3203</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1163,21 +1176,24 @@
         <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I4">
         <v>60</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:11">
+    <row r="5" ht="28" spans="1:12">
       <c r="A5">
         <v>33001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1189,13 +1205,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5">
         <v>120</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -1124,7 +1124,7 @@
         <v>60</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="29" customHeight="1" spans="1:12">
@@ -1185,7 +1185,7 @@
         <v>20</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:12">
@@ -1214,7 +1214,7 @@
         <v>120</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -97,7 +97,7 @@
     <t>一叶知秋</t>
   </si>
   <si>
-    <t>角色获得属性三（角色属性一/2）点</t>
+    <t>蒂娜获得属性三（蒂娜属性一/2）点</t>
   </si>
   <si>
     <t>addNatureByOther(3,1)</t>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>id</t>
   </si>
@@ -82,13 +82,13 @@
     <t>属性三提升{nature3}点，下回合属性加成提升50%</t>
   </si>
   <si>
-    <t>changeProperty(1.5)</t>
+    <t>addNatureAtSum(30,3);changeProperty(1.5)</t>
   </si>
   <si>
     <t>亭亭如盖</t>
   </si>
   <si>
-    <t>属性三提升{nature3}点，下回合随机获得一张普通功能牌</t>
+    <t>属性三提升{nature3}点，随机获得一张普通功能牌</t>
   </si>
   <si>
     <t>addRandomCard(2,1,1)</t>
@@ -1147,14 +1147,12 @@
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
+      <c r="J3"/>
       <c r="L3">
         <v>4</v>
       </c>
@@ -1178,12 +1176,13 @@
       <c r="F4" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
       <c r="I4">
         <v>60</v>
       </c>
-      <c r="J4" t="s">
-        <v>20</v>
-      </c>
+      <c r="J4"/>
       <c r="L4">
         <v>2</v>
       </c>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -88,7 +88,7 @@
     <t>亭亭如盖</t>
   </si>
   <si>
-    <t>属性三提升{nature3}点，随机获得一张普通功能牌</t>
+    <t>属性三提升{nature3}点，本回合随机获得一张普通功能牌</t>
   </si>
   <si>
     <t>addRandomCard(2,1,1)</t>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -67,6 +67,9 @@
     <t>dialog</t>
   </si>
   <si>
+    <t>eventDialog</t>
+  </si>
+  <si>
     <t>风过疏竹</t>
   </si>
   <si>
@@ -76,6 +79,9 @@
     <t>addNatureAtSum(30,3)</t>
   </si>
   <si>
+    <t>event001</t>
+  </si>
+  <si>
     <t>春风又生</t>
   </si>
   <si>
@@ -85,6 +91,9 @@
     <t>addNatureAtSum(30,3);changeProperty(1.5)</t>
   </si>
   <si>
+    <t>event002</t>
+  </si>
+  <si>
     <t>亭亭如盖</t>
   </si>
   <si>
@@ -94,6 +103,9 @@
     <t>addRandomCard(2,1,1)</t>
   </si>
   <si>
+    <t>event003</t>
+  </si>
+  <si>
     <t>一叶知秋</t>
   </si>
   <si>
@@ -101,6 +113,9 @@
   </si>
   <si>
     <t>addNatureByOther(3,1)</t>
+  </si>
+  <si>
+    <t>event004</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1064,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="18.0909090909091" customWidth="1"/>
@@ -1058,9 +1073,10 @@
     <col min="8" max="8" width="11.1818181818182" customWidth="1"/>
     <col min="9" max="9" width="15.5454545454545" customWidth="1"/>
     <col min="10" max="10" width="17.9090909090909" customWidth="1"/>
+    <col min="13" max="13" width="15.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1097,13 +1113,16 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" ht="17.5" spans="1:12">
+    <row r="2" ht="17.5" spans="1:13">
       <c r="A2">
         <v>31001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1115,10 +1134,10 @@
         <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2">
         <v>60</v>
@@ -1126,13 +1145,16 @@
       <c r="L2">
         <v>3</v>
       </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" ht="29" customHeight="1" spans="1:12">
+    <row r="3" ht="29" customHeight="1" spans="1:13">
       <c r="A3">
         <v>32002</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1144,25 +1166,27 @@
         <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
-      <c r="J3"/>
       <c r="L3">
         <v>4</v>
       </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:12">
+    <row r="4" ht="34" customHeight="1" spans="1:13">
       <c r="A4">
-        <v>3203</v>
+        <v>32003</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1174,25 +1198,27 @@
         <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I4">
         <v>60</v>
       </c>
-      <c r="J4"/>
       <c r="L4">
         <v>2</v>
       </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="5" ht="28" spans="1:12">
+    <row r="5" ht="28" spans="1:13">
       <c r="A5">
         <v>33001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1204,16 +1230,19 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I5">
         <v>120</v>
       </c>
       <c r="L5">
         <v>12</v>
+      </c>
+      <c r="M5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>id</t>
   </si>
@@ -49,6 +49,9 @@
     <t>description</t>
   </si>
   <si>
+    <t>text</t>
+  </si>
+  <si>
     <t>trigger</t>
   </si>
   <si>
@@ -70,49 +73,156 @@
     <t>eventDialog</t>
   </si>
   <si>
-    <t>风过疏竹</t>
-  </si>
-  <si>
-    <t>属性三提升{nature3}点</t>
-  </si>
-  <si>
-    <t>addNatureAtSum(30,3)</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>风过疏竹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事件）</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 属性三提升{nature3}点</t>
+  </si>
+  <si>
+    <t>卡牌介绍占坑</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(30,3);triggerEventDialogue(event001)</t>
   </si>
   <si>
     <t>event001</t>
   </si>
   <si>
-    <t>春风又生</t>
-  </si>
-  <si>
-    <t>属性三提升{nature3}点，下回合属性加成提升50%</t>
-  </si>
-  <si>
-    <t>addNatureAtSum(30,3);changeProperty(1.5)</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>春风又生</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事件）</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 属性三提升{nature3}点，下回合属性加成提升50%</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(30,3);changeProperty(1.5);triggerEventDialogue(event002)</t>
   </si>
   <si>
     <t>event002</t>
   </si>
   <si>
-    <t>亭亭如盖</t>
-  </si>
-  <si>
-    <t>属性三提升{nature3}点，本回合随机获得一张普通功能牌</t>
-  </si>
-  <si>
-    <t>addRandomCard(2,1,1)</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亭亭如盖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事件）</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 属性三提升{nature3}点，本回合随机获得一张普通功能牌</t>
+  </si>
+  <si>
+    <t>addRandomCard(2,1,1);triggerEventDialogue(event001)</t>
   </si>
   <si>
     <t>event003</t>
   </si>
   <si>
-    <t>一叶知秋</t>
-  </si>
-  <si>
-    <t>蒂娜获得属性三（蒂娜属性一/2）点</t>
-  </si>
-  <si>
-    <t>addNatureByOther(3,1)</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一叶知秋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事件）</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 蒂娜获得属性三（蒂娜属性一/2）点</t>
+  </si>
+  <si>
+    <t>addNatureByOther(3,1);triggerEventDialogue(event001)</t>
   </si>
   <si>
     <t>event004</t>
@@ -128,12 +238,162 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -141,150 +401,6 @@
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1064,19 +1180,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="18.0909090909091" customWidth="1"/>
     <col min="6" max="6" width="28.1818181818182" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.4545454545455" customWidth="1"/>
-    <col min="8" max="8" width="11.1818181818182" customWidth="1"/>
-    <col min="9" max="9" width="15.5454545454545" customWidth="1"/>
-    <col min="10" max="10" width="17.9090909090909" customWidth="1"/>
-    <col min="13" max="13" width="15.0909090909091" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="12.4545454545455" customWidth="1"/>
+    <col min="9" max="9" width="11.1818181818182" customWidth="1"/>
+    <col min="10" max="10" width="15.5454545454545" customWidth="1"/>
+    <col min="11" max="11" width="17.9090909090909" customWidth="1"/>
+    <col min="14" max="14" width="15.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1104,7 +1221,7 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1116,13 +1233,16 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" ht="17.5" spans="1:13">
+    <row r="2" ht="42" spans="1:14">
       <c r="A2">
         <v>31001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1134,27 +1254,30 @@
         <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2">
         <v>60</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>3</v>
       </c>
-      <c r="M2" t="s">
-        <v>16</v>
+      <c r="N2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" ht="29" customHeight="1" spans="1:13">
+    <row r="3" ht="29" customHeight="1" spans="1:14">
       <c r="A3">
         <v>32002</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1166,27 +1289,30 @@
         <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3">
         <v>60</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>4</v>
       </c>
-      <c r="M3" t="s">
-        <v>20</v>
+      <c r="N3" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:13">
+    <row r="4" ht="34" customHeight="1" spans="1:14">
       <c r="A4">
         <v>32003</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1198,27 +1324,30 @@
         <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4">
         <v>60</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>2</v>
       </c>
-      <c r="M4" t="s">
-        <v>24</v>
+      <c r="N4" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:13">
+    <row r="5" ht="42" spans="1:14">
       <c r="A5">
         <v>33001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1230,19 +1359,22 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5">
         <v>120</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>12</v>
       </c>
-      <c r="M5" t="s">
-        <v>28</v>
+      <c r="N5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -73,33 +73,7 @@
     <t>eventDialog</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>风过疏竹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事件）</t>
-    </r>
+    <t>一起打乒乓球吧</t>
   </si>
   <si>
     <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 属性三提升{nature3}点</t>
@@ -114,33 +88,7 @@
     <t>event001</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>春风又生</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事件）</t>
-    </r>
+    <t>乐队jam</t>
   </si>
   <si>
     <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 属性三提升{nature3}点，下回合属性加成提升50%</t>
@@ -152,33 +100,7 @@
     <t>event002</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>亭亭如盖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事件）</t>
-    </r>
+    <t>辅导作业</t>
   </si>
   <si>
     <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 属性三提升{nature3}点，本回合随机获得一张普通功能牌</t>
@@ -190,33 +112,7 @@
     <t>event003</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>一叶知秋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事件）</t>
-    </r>
+    <t>livehouse</t>
   </si>
   <si>
     <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 蒂娜获得属性三（蒂娜属性一/2）点</t>
@@ -238,7 +134,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,12 +291,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>text</t>
+  </si>
+  <si>
+    <t>prompt</t>
   </si>
   <si>
     <t>trigger</t>
@@ -1070,20 +1073,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="18.0909090909091" customWidth="1"/>
     <col min="6" max="6" width="28.1818181818182" style="1" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="12.4545454545455" customWidth="1"/>
-    <col min="9" max="9" width="11.1818181818182" customWidth="1"/>
-    <col min="10" max="10" width="15.5454545454545" customWidth="1"/>
-    <col min="11" max="11" width="17.9090909090909" customWidth="1"/>
-    <col min="14" max="14" width="15.0909090909091" customWidth="1"/>
+    <col min="8" max="9" width="12.4545454545455" customWidth="1"/>
+    <col min="10" max="10" width="11.1818181818182" customWidth="1"/>
+    <col min="11" max="11" width="15.5454545454545" customWidth="1"/>
+    <col min="12" max="12" width="17.9090909090909" customWidth="1"/>
+    <col min="15" max="15" width="15.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1114,7 +1117,7 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -1126,13 +1129,16 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" ht="42" spans="1:14">
+    <row r="2" ht="42" spans="1:15">
       <c r="A2">
         <v>31001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1144,30 +1150,33 @@
         <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="J2">
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2">
         <v>60</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>3</v>
       </c>
-      <c r="N2" t="s">
-        <v>18</v>
+      <c r="O2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" ht="29" customHeight="1" spans="1:14">
+    <row r="3" ht="29" customHeight="1" spans="1:15">
       <c r="A3">
         <v>32002</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1179,30 +1188,33 @@
         <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3">
+        <v>17</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3">
         <v>60</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>4</v>
       </c>
-      <c r="N3" t="s">
-        <v>22</v>
+      <c r="O3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:14">
+    <row r="4" ht="34" customHeight="1" spans="1:15">
       <c r="A4">
         <v>32003</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1214,30 +1226,33 @@
         <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4">
+        <v>17</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4">
         <v>60</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>2</v>
       </c>
-      <c r="N4" t="s">
-        <v>26</v>
+      <c r="O4" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="5" ht="42" spans="1:14">
+    <row r="5" ht="42" spans="1:15">
       <c r="A5">
         <v>33001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1249,22 +1264,25 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5">
+        <v>17</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5">
         <v>120</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>12</v>
       </c>
-      <c r="N5" t="s">
-        <v>30</v>
+      <c r="O5" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>sale</t>
+  </si>
+  <si>
+    <t>sell</t>
   </si>
   <si>
     <t>nextTurn</t>
@@ -1073,7 +1076,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="18.0909090909091" customWidth="1"/>
@@ -1082,11 +1085,11 @@
     <col min="8" max="9" width="12.4545454545455" customWidth="1"/>
     <col min="10" max="10" width="11.1818181818182" customWidth="1"/>
     <col min="11" max="11" width="15.5454545454545" customWidth="1"/>
-    <col min="12" max="12" width="17.9090909090909" customWidth="1"/>
-    <col min="15" max="15" width="15.0909090909091" customWidth="1"/>
+    <col min="12" max="13" width="17.9090909090909" customWidth="1"/>
+    <col min="16" max="16" width="15.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1132,13 +1135,16 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" ht="42" spans="1:15">
+    <row r="2" ht="42" spans="1:16">
       <c r="A2">
         <v>31001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1150,33 +1156,36 @@
         <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2">
         <v>4</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2">
         <v>60</v>
       </c>
-      <c r="N2">
+      <c r="L2">
+        <v>40</v>
+      </c>
+      <c r="O2">
         <v>3</v>
       </c>
-      <c r="O2" t="s">
-        <v>19</v>
+      <c r="P2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3" ht="29" customHeight="1" spans="1:15">
+    <row r="3" ht="29" customHeight="1" spans="1:16">
       <c r="A3">
         <v>32002</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1188,33 +1197,36 @@
         <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3">
         <v>4</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3">
         <v>60</v>
       </c>
-      <c r="N3">
+      <c r="L3">
+        <v>40</v>
+      </c>
+      <c r="O3">
         <v>4</v>
       </c>
-      <c r="O3" t="s">
-        <v>23</v>
+      <c r="P3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:15">
+    <row r="4" ht="34" customHeight="1" spans="1:16">
       <c r="A4">
         <v>32003</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1226,33 +1238,36 @@
         <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4">
         <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K4">
         <v>60</v>
       </c>
-      <c r="N4">
+      <c r="L4">
+        <v>40</v>
+      </c>
+      <c r="O4">
         <v>2</v>
       </c>
-      <c r="O4" t="s">
-        <v>27</v>
+      <c r="P4" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" ht="42" spans="1:15">
+    <row r="5" ht="42" spans="1:16">
       <c r="A5">
         <v>33001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1264,25 +1279,28 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K5">
         <v>120</v>
       </c>
-      <c r="N5">
+      <c r="L5">
+        <v>80</v>
+      </c>
+      <c r="O5">
         <v>12</v>
       </c>
-      <c r="O5" t="s">
-        <v>31</v>
+      <c r="P5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>17</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>26</v>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -1168,10 +1168,11 @@
         <v>19</v>
       </c>
       <c r="K2">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L2">
-        <v>40</v>
+        <f>K2*0.8</f>
+        <v>24</v>
       </c>
       <c r="O2">
         <v>3</v>
@@ -1212,7 +1213,8 @@
         <v>60</v>
       </c>
       <c r="L3">
-        <v>40</v>
+        <f>K3*0.8</f>
+        <v>48</v>
       </c>
       <c r="O3">
         <v>4</v>
@@ -1253,7 +1255,8 @@
         <v>60</v>
       </c>
       <c r="L4">
-        <v>40</v>
+        <f>K4*0.8</f>
+        <v>48</v>
       </c>
       <c r="O4">
         <v>2</v>
@@ -1294,7 +1297,8 @@
         <v>120</v>
       </c>
       <c r="L5">
-        <v>80</v>
+        <f>K5*0.8</f>
+        <v>96</v>
       </c>
       <c r="O5">
         <v>12</v>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -79,10 +79,10 @@
     <t>eventDialog</t>
   </si>
   <si>
-    <t>一起打乒乓球吧</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 属性三提升{nature3}点</t>
+    <t>乒乓球初级训练</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  属性三提升{nature3}点</t>
   </si>
   <si>
     <t>卡牌介绍占坑</t>
@@ -94,10 +94,10 @@
     <t>event001</t>
   </si>
   <si>
-    <t>乐队jam</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 属性三提升{nature3}点，下回合属性加成提升50%</t>
+    <t>一起手工</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  属性三提升{nature3}点，下回合属性加成提升50%</t>
   </si>
   <si>
     <t>addNatureAtSum(30,3);changeProperty(1.5);triggerEventDialogue(event002)</t>
@@ -106,10 +106,10 @@
     <t>event002</t>
   </si>
   <si>
-    <t>辅导作业</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 属性三提升{nature3}点，本回合随机获得一张普通功能牌</t>
+    <t>乒乓球高级训练</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  属性三提升{nature3}点，本回合随机获得一张普通功能牌</t>
   </si>
   <si>
     <t>addRandomCard(2,1,1);triggerEventDialogue(event001)</t>
@@ -118,13 +118,13 @@
     <t>event003</t>
   </si>
   <si>
-    <t>livehouse</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 蒂娜获得属性三（蒂娜属性一/2）点</t>
-  </si>
-  <si>
-    <t>addNatureByOther(3,1);triggerEventDialogue(event001)</t>
+    <t>玩音乐</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  蒂娜获得属性三（蒂娜属性一/2）点</t>
+  </si>
+  <si>
+    <t>addNatureByOther(1,3);triggerEventDialogue(event001)</t>
   </si>
   <si>
     <t>event004</t>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -82,7 +82,7 @@
     <t>乒乓球初级训练</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  属性三提升{nature3}点</t>
+    <t>好感三提升{nature3}点</t>
   </si>
   <si>
     <t>卡牌介绍占坑</t>
@@ -97,7 +97,7 @@
     <t>一起手工</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  属性三提升{nature3}点，下回合属性加成提升50%</t>
+    <t>好感三提升{nature3}点，下回合好感加成提升50%</t>
   </si>
   <si>
     <t>addNatureAtSum(30,3);changeProperty(1.5);triggerEventDialogue(event002)</t>
@@ -109,7 +109,7 @@
     <t>乒乓球高级训练</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  属性三提升{nature3}点，本回合随机获得一张普通功能牌</t>
+    <t>好感三提升{nature3}点，本回合随机获得一张普通功能牌</t>
   </si>
   <si>
     <t>addRandomCard(2,1,1);triggerEventDialogue(event001)</t>
@@ -121,7 +121,7 @@
     <t>玩音乐</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  蒂娜获得属性三（蒂娜属性一/2）点</t>
+    <t>蒂娜获得好感三（蒂娜好感一/2）点</t>
   </si>
   <si>
     <t>addNatureByOther(1,3);triggerEventDialogue(event001)</t>
@@ -1139,7 +1139,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="42" spans="1:16">
+    <row r="2" ht="15" spans="1:16">
       <c r="A2">
         <v>31001</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" ht="42" spans="1:16">
+    <row r="5" ht="28" spans="1:16">
       <c r="A5">
         <v>33001</v>
       </c>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>id</t>
   </si>
@@ -85,7 +85,7 @@
     <t>好感三提升{nature3}点</t>
   </si>
   <si>
-    <t>卡牌介绍占坑</t>
+    <t>介绍了如何指导伴侣进行乒乓球训练</t>
   </si>
   <si>
     <t>addNatureAtSum(30,3);triggerEventDialogue(event001)</t>
@@ -94,12 +94,15 @@
     <t>event001</t>
   </si>
   <si>
-    <t>一起手工</t>
+    <t>手工教程</t>
   </si>
   <si>
     <t>好感三提升{nature3}点，下回合好感加成提升50%</t>
   </si>
   <si>
+    <t>介绍了如何指导初学者进行手工</t>
+  </si>
+  <si>
     <t>addNatureAtSum(30,3);changeProperty(1.5);triggerEventDialogue(event002)</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>好感三提升{nature3}点，本回合随机获得一张普通功能牌</t>
   </si>
   <si>
+    <t>介绍了如何指导伴侣进行更高级的乒乓球训练</t>
+  </si>
+  <si>
     <t>addRandomCard(2,1,1);triggerEventDialogue(event001)</t>
   </si>
   <si>
@@ -122,6 +128,9 @@
   </si>
   <si>
     <t>蒂娜获得好感三（蒂娜好感一/2）点</t>
+  </si>
+  <si>
+    <t>介绍了各个乐器在演奏中如何进行配合，强调了演出者们的联结</t>
   </si>
   <si>
     <t>addNatureByOther(1,3);triggerEventDialogue(event001)</t>
@@ -749,7 +758,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -761,6 +770,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1081,7 +1093,7 @@
   <cols>
     <col min="2" max="2" width="18.0909090909091" customWidth="1"/>
     <col min="6" max="6" width="28.1818181818182" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="7" max="7" width="15" style="1" customWidth="1"/>
     <col min="8" max="9" width="12.4545454545455" customWidth="1"/>
     <col min="10" max="10" width="11.1818181818182" customWidth="1"/>
     <col min="11" max="11" width="15.5454545454545" customWidth="1"/>
@@ -1108,7 +1120,7 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -1139,11 +1151,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:16">
+    <row r="2" ht="42" spans="1:16">
       <c r="A2">
         <v>31001</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C2">
@@ -1158,7 +1170,7 @@
       <c r="F2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H2">
@@ -1185,7 +1197,7 @@
       <c r="A3">
         <v>32002</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C3">
@@ -1200,14 +1212,14 @@
       <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
-        <v>18</v>
+      <c r="G3" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="H3">
         <v>4</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3">
         <v>60</v>
@@ -1220,15 +1232,15 @@
         <v>4</v>
       </c>
       <c r="P3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:16">
+    <row r="4" ht="51" customHeight="1" spans="1:16">
       <c r="A4">
         <v>32003</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>25</v>
+      <c r="B4" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1240,16 +1252,16 @@
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
+        <v>27</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="H4">
         <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K4">
         <v>60</v>
@@ -1262,15 +1274,15 @@
         <v>2</v>
       </c>
       <c r="P4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:16">
+    <row r="5" ht="56" spans="1:16">
       <c r="A5">
         <v>33001</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>29</v>
+      <c r="B5" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1282,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K5">
         <v>120</v>
@@ -1304,7 +1316,7 @@
         <v>12</v>
       </c>
       <c r="P5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/eventCard.xlsx
+++ b/eventCard.xlsx
@@ -88,7 +88,7 @@
     <t>介绍了如何指导伴侣进行乒乓球训练</t>
   </si>
   <si>
-    <t>addNatureAtSum(30,3);triggerEventDialogue(event001)</t>
+    <t>addNatureAtSum(30,3);triggerEventDialogue(event003)</t>
   </si>
   <si>
     <t>event001</t>
@@ -103,7 +103,7 @@
     <t>介绍了如何指导初学者进行手工</t>
   </si>
   <si>
-    <t>addNatureAtSum(30,3);changeProperty(1.5);triggerEventDialogue(event002)</t>
+    <t>addNatureAtSum(30,3);changeProperty(1.5);triggerEventDialogue(event001)</t>
   </si>
   <si>
     <t>event002</t>
@@ -118,7 +118,7 @@
     <t>介绍了如何指导伴侣进行更高级的乒乓球训练</t>
   </si>
   <si>
-    <t>addRandomCard(2,1,1);triggerEventDialogue(event001)</t>
+    <t>addRandomCard(2,1,1);triggerEventDialogue(event004)</t>
   </si>
   <si>
     <t>event003</t>
@@ -133,7 +133,7 @@
     <t>介绍了各个乐器在演奏中如何进行配合，强调了演出者们的联结</t>
   </si>
   <si>
-    <t>addNatureByOther(1,3);triggerEventDialogue(event001)</t>
+    <t>addNatureByOther(1,3);triggerEventDialogue(event002)</t>
   </si>
   <si>
     <t>event004</t>
